--- a/PYTHON/DATA_ANALYSIS/VALUO/data_strukturovana/___ALL/1/cadastre_report_6_2024 (9).xlsx
+++ b/PYTHON/DATA_ANALYSIS/VALUO/data_strukturovana/___ALL/1/cadastre_report_6_2024 (9).xlsx
@@ -1,21 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3ad31658eb0d26ad/Dokumenty/PROG/PYTHON/DATA_ANALYSIS/VALUO/data_strukturovana/___ALL/1/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_85ADD5D78B1C897C30B37D5FF6CEC02DABF23748" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08DB821F-EA78-4B30-9AE4-D2D510AB18B1}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView minimized="1" xWindow="4224" yWindow="4224" windowWidth="18816" windowHeight="8736" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029" calcCompleted="0" forceFullCalc="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2116" uniqueCount="547">
   <si>
     <t>Číslo vkladu</t>
   </si>
@@ -1661,16 +1679,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00_-"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -1697,14 +1711,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1994,14 +2016,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P176"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="27.44140625" customWidth="1"/>
+    <col min="6" max="6" width="54.44140625" customWidth="1"/>
+    <col min="7" max="7" width="41.77734375" customWidth="1"/>
+    <col min="8" max="8" width="30.33203125" customWidth="1"/>
+    <col min="11" max="11" width="55.6640625" customWidth="1"/>
+    <col min="12" max="12" width="200.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2051,7 +2078,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2101,7 +2128,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2151,7 +2178,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -2201,7 +2228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -2251,7 +2278,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -2301,7 +2328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -2351,7 +2378,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -2380,7 +2407,7 @@
         <v>23</v>
       </c>
       <c r="J8" s="1">
-        <v>87.0</v>
+        <v>87</v>
       </c>
       <c r="K8" t="s">
         <v>24</v>
@@ -2401,7 +2428,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -2430,7 +2457,7 @@
         <v>23</v>
       </c>
       <c r="J9" s="1">
-        <v>113.0</v>
+        <v>113</v>
       </c>
       <c r="K9" t="s">
         <v>59</v>
@@ -2451,7 +2478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -2480,7 +2507,7 @@
         <v>23</v>
       </c>
       <c r="J10" s="1">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="K10" t="s">
         <v>59</v>
@@ -2501,7 +2528,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -2530,7 +2557,7 @@
         <v>23</v>
       </c>
       <c r="J11" s="1">
-        <v>277.0</v>
+        <v>277</v>
       </c>
       <c r="K11" t="s">
         <v>59</v>
@@ -2551,7 +2578,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>68</v>
       </c>
@@ -2601,7 +2628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>68</v>
       </c>
@@ -2651,7 +2678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>74</v>
       </c>
@@ -2680,7 +2707,7 @@
         <v>23</v>
       </c>
       <c r="J14" s="1">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="K14" t="s">
         <v>24</v>
@@ -2701,7 +2728,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>80</v>
       </c>
@@ -2751,7 +2778,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>84</v>
       </c>
@@ -2801,7 +2828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>84</v>
       </c>
@@ -2851,7 +2878,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>88</v>
       </c>
@@ -2880,7 +2907,7 @@
         <v>23</v>
       </c>
       <c r="J18" s="1">
-        <v>126.0</v>
+        <v>126</v>
       </c>
       <c r="K18" t="s">
         <v>59</v>
@@ -2901,7 +2928,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>88</v>
       </c>
@@ -2930,7 +2957,7 @@
         <v>23</v>
       </c>
       <c r="J19" s="1">
-        <v>945.0</v>
+        <v>945</v>
       </c>
       <c r="K19" t="s">
         <v>59</v>
@@ -2951,7 +2978,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>95</v>
       </c>
@@ -2980,7 +3007,7 @@
         <v>23</v>
       </c>
       <c r="J20" s="1">
-        <v>72.1</v>
+        <v>72.099999999999994</v>
       </c>
       <c r="K20" t="s">
         <v>24</v>
@@ -3001,7 +3028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>98</v>
       </c>
@@ -3051,7 +3078,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>102</v>
       </c>
@@ -3101,7 +3128,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>106</v>
       </c>
@@ -3151,7 +3178,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>106</v>
       </c>
@@ -3201,7 +3228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>106</v>
       </c>
@@ -3230,7 +3257,7 @@
         <v>23</v>
       </c>
       <c r="J25" s="1">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="K25" t="s">
         <v>24</v>
@@ -3251,7 +3278,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>113</v>
       </c>
@@ -3301,7 +3328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>118</v>
       </c>
@@ -3351,7 +3378,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>122</v>
       </c>
@@ -3380,7 +3407,7 @@
         <v>23</v>
       </c>
       <c r="J28" s="1">
-        <v>498.0</v>
+        <v>498</v>
       </c>
       <c r="K28" t="s">
         <v>59</v>
@@ -3401,7 +3428,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>127</v>
       </c>
@@ -3451,7 +3478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>131</v>
       </c>
@@ -3501,7 +3528,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>135</v>
       </c>
@@ -3530,7 +3557,7 @@
         <v>23</v>
       </c>
       <c r="J31" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K31" t="s">
         <v>59</v>
@@ -3551,7 +3578,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>135</v>
       </c>
@@ -3580,7 +3607,7 @@
         <v>23</v>
       </c>
       <c r="J32" s="1">
-        <v>912.0</v>
+        <v>912</v>
       </c>
       <c r="K32" t="s">
         <v>59</v>
@@ -3601,7 +3628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>142</v>
       </c>
@@ -3651,7 +3678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>142</v>
       </c>
@@ -3680,7 +3707,7 @@
         <v>23</v>
       </c>
       <c r="J34" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="K34" t="s">
         <v>59</v>
@@ -3701,7 +3728,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>142</v>
       </c>
@@ -3730,7 +3757,7 @@
         <v>23</v>
       </c>
       <c r="J35" s="1">
-        <v>268.0</v>
+        <v>268</v>
       </c>
       <c r="K35" t="s">
         <v>59</v>
@@ -3751,7 +3778,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>142</v>
       </c>
@@ -3780,7 +3807,7 @@
         <v>23</v>
       </c>
       <c r="J36" s="1">
-        <v>729.0</v>
+        <v>729</v>
       </c>
       <c r="K36" t="s">
         <v>59</v>
@@ -3801,7 +3828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>154</v>
       </c>
@@ -3851,7 +3878,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>159</v>
       </c>
@@ -3901,7 +3928,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>159</v>
       </c>
@@ -3951,7 +3978,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>163</v>
       </c>
@@ -4001,7 +4028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>163</v>
       </c>
@@ -4051,7 +4078,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>167</v>
       </c>
@@ -4080,7 +4107,7 @@
         <v>23</v>
       </c>
       <c r="J42" s="1">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="K42" t="s">
         <v>24</v>
@@ -4101,7 +4128,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>172</v>
       </c>
@@ -4130,7 +4157,7 @@
         <v>23</v>
       </c>
       <c r="J43" s="1">
-        <v>213.0</v>
+        <v>213</v>
       </c>
       <c r="K43" t="s">
         <v>176</v>
@@ -4151,7 +4178,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>172</v>
       </c>
@@ -4180,7 +4207,7 @@
         <v>23</v>
       </c>
       <c r="J44" s="1">
-        <v>729.0</v>
+        <v>729</v>
       </c>
       <c r="K44" t="s">
         <v>59</v>
@@ -4201,7 +4228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>172</v>
       </c>
@@ -4230,7 +4257,7 @@
         <v>23</v>
       </c>
       <c r="J45" s="1">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="K45" t="s">
         <v>59</v>
@@ -4251,7 +4278,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>172</v>
       </c>
@@ -4280,7 +4307,7 @@
         <v>23</v>
       </c>
       <c r="J46" s="1">
-        <v>299.0</v>
+        <v>299</v>
       </c>
       <c r="K46" t="s">
         <v>59</v>
@@ -4301,7 +4328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>182</v>
       </c>
@@ -4351,7 +4378,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>185</v>
       </c>
@@ -4401,7 +4428,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>189</v>
       </c>
@@ -4430,7 +4457,7 @@
         <v>23</v>
       </c>
       <c r="J49" s="1">
-        <v>355.0</v>
+        <v>355</v>
       </c>
       <c r="K49" t="s">
         <v>59</v>
@@ -4451,7 +4478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>194</v>
       </c>
@@ -4501,7 +4528,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>194</v>
       </c>
@@ -4530,7 +4557,7 @@
         <v>23</v>
       </c>
       <c r="J51" s="1">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="K51" t="s">
         <v>59</v>
@@ -4551,7 +4578,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:16">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>194</v>
       </c>
@@ -4580,7 +4607,7 @@
         <v>23</v>
       </c>
       <c r="J52" s="1">
-        <v>268.0</v>
+        <v>268</v>
       </c>
       <c r="K52" t="s">
         <v>59</v>
@@ -4601,7 +4628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:16">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>194</v>
       </c>
@@ -4630,7 +4657,7 @@
         <v>23</v>
       </c>
       <c r="J53" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="K53" t="s">
         <v>59</v>
@@ -4651,7 +4678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:16">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>194</v>
       </c>
@@ -4680,7 +4707,7 @@
         <v>23</v>
       </c>
       <c r="J54" s="1">
-        <v>729.0</v>
+        <v>729</v>
       </c>
       <c r="K54" t="s">
         <v>59</v>
@@ -4701,7 +4728,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:16">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>201</v>
       </c>
@@ -4751,7 +4778,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:16">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>204</v>
       </c>
@@ -4780,7 +4807,7 @@
         <v>23</v>
       </c>
       <c r="J56" s="1">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="K56" t="s">
         <v>24</v>
@@ -4801,7 +4828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:16">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>209</v>
       </c>
@@ -4851,7 +4878,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:16">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>212</v>
       </c>
@@ -4901,7 +4928,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:16">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>215</v>
       </c>
@@ -4930,7 +4957,7 @@
         <v>23</v>
       </c>
       <c r="J59" s="1">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="K59" t="s">
         <v>24</v>
@@ -4951,7 +4978,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:16">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>220</v>
       </c>
@@ -5001,7 +5028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:16">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>225</v>
       </c>
@@ -5051,7 +5078,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:16">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>230</v>
       </c>
@@ -5101,7 +5128,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:16">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>234</v>
       </c>
@@ -5130,7 +5157,7 @@
         <v>23</v>
       </c>
       <c r="J63" s="1">
-        <v>245.0</v>
+        <v>245</v>
       </c>
       <c r="K63" t="s">
         <v>59</v>
@@ -5151,7 +5178,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:16">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>234</v>
       </c>
@@ -5180,7 +5207,7 @@
         <v>23</v>
       </c>
       <c r="J64" s="1">
-        <v>489.0</v>
+        <v>489</v>
       </c>
       <c r="K64" t="s">
         <v>59</v>
@@ -5201,7 +5228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:16">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>234</v>
       </c>
@@ -5230,7 +5257,7 @@
         <v>23</v>
       </c>
       <c r="J65" s="1">
-        <v>518.0</v>
+        <v>518</v>
       </c>
       <c r="K65" t="s">
         <v>59</v>
@@ -5251,7 +5278,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:16">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>243</v>
       </c>
@@ -5301,7 +5328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:16">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>243</v>
       </c>
@@ -5330,7 +5357,7 @@
         <v>23</v>
       </c>
       <c r="J67" s="1">
-        <v>268.0</v>
+        <v>268</v>
       </c>
       <c r="K67" t="s">
         <v>59</v>
@@ -5351,7 +5378,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:16">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>243</v>
       </c>
@@ -5380,7 +5407,7 @@
         <v>23</v>
       </c>
       <c r="J68" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="K68" t="s">
         <v>59</v>
@@ -5401,7 +5428,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:16">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>243</v>
       </c>
@@ -5430,7 +5457,7 @@
         <v>23</v>
       </c>
       <c r="J69" s="1">
-        <v>729.0</v>
+        <v>729</v>
       </c>
       <c r="K69" t="s">
         <v>59</v>
@@ -5451,7 +5478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:16">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>247</v>
       </c>
@@ -5501,7 +5528,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:16">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>250</v>
       </c>
@@ -5551,7 +5578,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:16">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>250</v>
       </c>
@@ -5580,7 +5607,7 @@
         <v>23</v>
       </c>
       <c r="J72" s="1">
-        <v>268.0</v>
+        <v>268</v>
       </c>
       <c r="K72" t="s">
         <v>59</v>
@@ -5601,7 +5628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:16">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>250</v>
       </c>
@@ -5630,7 +5657,7 @@
         <v>23</v>
       </c>
       <c r="J73" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="K73" t="s">
         <v>59</v>
@@ -5651,7 +5678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:16">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>250</v>
       </c>
@@ -5680,7 +5707,7 @@
         <v>23</v>
       </c>
       <c r="J74" s="1">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="K74" t="s">
         <v>59</v>
@@ -5701,7 +5728,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:16">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>250</v>
       </c>
@@ -5730,7 +5757,7 @@
         <v>23</v>
       </c>
       <c r="J75" s="1">
-        <v>729.0</v>
+        <v>729</v>
       </c>
       <c r="K75" t="s">
         <v>59</v>
@@ -5751,7 +5778,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:16">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>256</v>
       </c>
@@ -5801,7 +5828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:16">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>261</v>
       </c>
@@ -5851,7 +5878,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:16">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>264</v>
       </c>
@@ -5901,7 +5928,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:16">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>264</v>
       </c>
@@ -5930,7 +5957,7 @@
         <v>23</v>
       </c>
       <c r="J79" s="1">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="K79" t="s">
         <v>24</v>
@@ -5951,7 +5978,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:16">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>264</v>
       </c>
@@ -6001,7 +6028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:16">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>271</v>
       </c>
@@ -6051,7 +6078,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:16">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>275</v>
       </c>
@@ -6101,7 +6128,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:16">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>278</v>
       </c>
@@ -6151,7 +6178,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="1:16">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>278</v>
       </c>
@@ -6180,7 +6207,7 @@
         <v>23</v>
       </c>
       <c r="J84" s="1">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="K84" t="s">
         <v>24</v>
@@ -6201,7 +6228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:16">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>278</v>
       </c>
@@ -6251,7 +6278,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:16">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>285</v>
       </c>
@@ -6301,7 +6328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:16">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>285</v>
       </c>
@@ -6351,7 +6378,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:16">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>285</v>
       </c>
@@ -6380,7 +6407,7 @@
         <v>23</v>
       </c>
       <c r="J88" s="1">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="K88" t="s">
         <v>24</v>
@@ -6401,7 +6428,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:16">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>290</v>
       </c>
@@ -6430,7 +6457,7 @@
         <v>23</v>
       </c>
       <c r="J89" s="1">
-        <v>73.1</v>
+        <v>73.099999999999994</v>
       </c>
       <c r="K89" t="s">
         <v>24</v>
@@ -6451,7 +6478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:16">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>290</v>
       </c>
@@ -6480,7 +6507,7 @@
         <v>23</v>
       </c>
       <c r="J90" s="1">
-        <v>2137.0</v>
+        <v>2137</v>
       </c>
       <c r="K90" t="s">
         <v>59</v>
@@ -6501,7 +6528,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:16">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>290</v>
       </c>
@@ -6530,7 +6557,7 @@
         <v>23</v>
       </c>
       <c r="J91" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="K91" t="s">
         <v>59</v>
@@ -6551,7 +6578,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:16">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>290</v>
       </c>
@@ -6580,7 +6607,7 @@
         <v>23</v>
       </c>
       <c r="J92" s="1">
-        <v>302.0</v>
+        <v>302</v>
       </c>
       <c r="K92" t="s">
         <v>59</v>
@@ -6601,7 +6628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:16">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>301</v>
       </c>
@@ -6630,7 +6657,7 @@
         <v>23</v>
       </c>
       <c r="J93" s="1">
-        <v>205.0</v>
+        <v>205</v>
       </c>
       <c r="K93" t="s">
         <v>59</v>
@@ -6651,7 +6678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:16">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>301</v>
       </c>
@@ -6680,7 +6707,7 @@
         <v>23</v>
       </c>
       <c r="J94" s="1">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="K94" t="s">
         <v>59</v>
@@ -6701,7 +6728,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:16">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>301</v>
       </c>
@@ -6730,7 +6757,7 @@
         <v>23</v>
       </c>
       <c r="J95" s="1">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="K95" t="s">
         <v>176</v>
@@ -6751,7 +6778,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:16">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>301</v>
       </c>
@@ -6780,7 +6807,7 @@
         <v>23</v>
       </c>
       <c r="J96" s="1">
-        <v>177.0</v>
+        <v>177</v>
       </c>
       <c r="K96" t="s">
         <v>59</v>
@@ -6801,7 +6828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:16">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>312</v>
       </c>
@@ -6851,7 +6878,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:16">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>317</v>
       </c>
@@ -6901,7 +6928,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:16">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>317</v>
       </c>
@@ -6930,7 +6957,7 @@
         <v>23</v>
       </c>
       <c r="J99" s="1">
-        <v>414.0</v>
+        <v>414</v>
       </c>
       <c r="K99" t="s">
         <v>59</v>
@@ -6951,7 +6978,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:16">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>317</v>
       </c>
@@ -6980,7 +7007,7 @@
         <v>23</v>
       </c>
       <c r="J100" s="1">
-        <v>314.0</v>
+        <v>314</v>
       </c>
       <c r="K100" t="s">
         <v>59</v>
@@ -7001,7 +7028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:16">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>317</v>
       </c>
@@ -7030,7 +7057,7 @@
         <v>23</v>
       </c>
       <c r="J101" s="1">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="K101" t="s">
         <v>59</v>
@@ -7051,7 +7078,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:16">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>317</v>
       </c>
@@ -7080,7 +7107,7 @@
         <v>23</v>
       </c>
       <c r="J102" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K102" t="s">
         <v>59</v>
@@ -7101,7 +7128,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:16">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>317</v>
       </c>
@@ -7130,7 +7157,7 @@
         <v>23</v>
       </c>
       <c r="J103" s="1">
-        <v>279.0</v>
+        <v>279</v>
       </c>
       <c r="K103" t="s">
         <v>59</v>
@@ -7151,7 +7178,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:16">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>317</v>
       </c>
@@ -7180,7 +7207,7 @@
         <v>23</v>
       </c>
       <c r="J104" s="1">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="K104" t="s">
         <v>59</v>
@@ -7201,7 +7228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:16">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>317</v>
       </c>
@@ -7230,7 +7257,7 @@
         <v>23</v>
       </c>
       <c r="J105" s="1">
-        <v>71.0</v>
+        <v>71</v>
       </c>
       <c r="K105" t="s">
         <v>59</v>
@@ -7251,7 +7278,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:16">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>317</v>
       </c>
@@ -7280,7 +7307,7 @@
         <v>23</v>
       </c>
       <c r="J106" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="K106" t="s">
         <v>59</v>
@@ -7301,7 +7328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:16">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>317</v>
       </c>
@@ -7330,7 +7357,7 @@
         <v>23</v>
       </c>
       <c r="J107" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="K107" t="s">
         <v>59</v>
@@ -7351,7 +7378,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:16">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>317</v>
       </c>
@@ -7380,7 +7407,7 @@
         <v>23</v>
       </c>
       <c r="J108" s="1">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="K108" t="s">
         <v>59</v>
@@ -7401,7 +7428,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:16">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>317</v>
       </c>
@@ -7430,7 +7457,7 @@
         <v>23</v>
       </c>
       <c r="J109" s="1">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="K109" t="s">
         <v>59</v>
@@ -7451,7 +7478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:16">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>317</v>
       </c>
@@ -7480,7 +7507,7 @@
         <v>23</v>
       </c>
       <c r="J110" s="1">
-        <v>3798.0</v>
+        <v>3798</v>
       </c>
       <c r="K110" t="s">
         <v>59</v>
@@ -7501,7 +7528,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:16">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>317</v>
       </c>
@@ -7530,7 +7557,7 @@
         <v>23</v>
       </c>
       <c r="J111" s="1">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="K111" t="s">
         <v>59</v>
@@ -7551,7 +7578,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:16">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>317</v>
       </c>
@@ -7580,7 +7607,7 @@
         <v>23</v>
       </c>
       <c r="J112" s="1">
-        <v>180.0</v>
+        <v>180</v>
       </c>
       <c r="K112" t="s">
         <v>59</v>
@@ -7601,7 +7628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:16">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>317</v>
       </c>
@@ -7630,7 +7657,7 @@
         <v>23</v>
       </c>
       <c r="J113" s="1">
-        <v>316.0</v>
+        <v>316</v>
       </c>
       <c r="K113" t="s">
         <v>59</v>
@@ -7651,7 +7678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:16">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>317</v>
       </c>
@@ -7680,7 +7707,7 @@
         <v>23</v>
       </c>
       <c r="J114" s="1">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="K114" t="s">
         <v>59</v>
@@ -7701,7 +7728,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:16">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>317</v>
       </c>
@@ -7730,7 +7757,7 @@
         <v>23</v>
       </c>
       <c r="J115" s="1">
-        <v>409.0</v>
+        <v>409</v>
       </c>
       <c r="K115" t="s">
         <v>59</v>
@@ -7751,7 +7778,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:16">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>317</v>
       </c>
@@ -7780,7 +7807,7 @@
         <v>23</v>
       </c>
       <c r="J116" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="K116" t="s">
         <v>59</v>
@@ -7801,7 +7828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:16">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>317</v>
       </c>
@@ -7830,7 +7857,7 @@
         <v>23</v>
       </c>
       <c r="J117" s="1">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="K117" t="s">
         <v>59</v>
@@ -7851,7 +7878,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:16">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>317</v>
       </c>
@@ -7880,7 +7907,7 @@
         <v>23</v>
       </c>
       <c r="J118" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="K118" t="s">
         <v>59</v>
@@ -7901,7 +7928,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:16">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>317</v>
       </c>
@@ -7930,7 +7957,7 @@
         <v>23</v>
       </c>
       <c r="J119" s="1">
-        <v>387.0</v>
+        <v>387</v>
       </c>
       <c r="K119" t="s">
         <v>59</v>
@@ -7951,7 +7978,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:16">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>317</v>
       </c>
@@ -7980,7 +8007,7 @@
         <v>23</v>
       </c>
       <c r="J120" s="1">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="K120" t="s">
         <v>59</v>
@@ -8001,7 +8028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:16">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>317</v>
       </c>
@@ -8030,7 +8057,7 @@
         <v>23</v>
       </c>
       <c r="J121" s="1">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="K121" t="s">
         <v>59</v>
@@ -8051,7 +8078,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:16">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>317</v>
       </c>
@@ -8080,7 +8107,7 @@
         <v>23</v>
       </c>
       <c r="J122" s="1">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="K122" t="s">
         <v>59</v>
@@ -8101,7 +8128,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:16">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>371</v>
       </c>
@@ -8130,7 +8157,7 @@
         <v>23</v>
       </c>
       <c r="J123" s="1">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="K123" t="s">
         <v>24</v>
@@ -8151,7 +8178,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:16">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>376</v>
       </c>
@@ -8180,7 +8207,7 @@
         <v>23</v>
       </c>
       <c r="J124" s="1">
-        <v>195.0</v>
+        <v>195</v>
       </c>
       <c r="K124" t="s">
         <v>59</v>
@@ -8201,7 +8228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="125" spans="1:16">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>376</v>
       </c>
@@ -8230,7 +8257,7 @@
         <v>23</v>
       </c>
       <c r="J125" s="1">
-        <v>1433.0</v>
+        <v>1433</v>
       </c>
       <c r="K125" t="s">
         <v>59</v>
@@ -8251,7 +8278,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:16">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>376</v>
       </c>
@@ -8280,7 +8307,7 @@
         <v>23</v>
       </c>
       <c r="J126" s="1">
-        <v>113.0</v>
+        <v>113</v>
       </c>
       <c r="K126" t="s">
         <v>59</v>
@@ -8301,7 +8328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:16">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>388</v>
       </c>
@@ -8351,7 +8378,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="128" spans="1:16">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>388</v>
       </c>
@@ -8380,7 +8407,7 @@
         <v>23</v>
       </c>
       <c r="J128" s="1">
-        <v>66.0</v>
+        <v>66</v>
       </c>
       <c r="K128" t="s">
         <v>24</v>
@@ -8401,7 +8428,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="129" spans="1:16">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>394</v>
       </c>
@@ -8451,7 +8478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:16">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>394</v>
       </c>
@@ -8480,7 +8507,7 @@
         <v>23</v>
       </c>
       <c r="J130" s="1">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="K130" t="s">
         <v>24</v>
@@ -8501,7 +8528,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="131" spans="1:16">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>399</v>
       </c>
@@ -8551,7 +8578,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:16">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>404</v>
       </c>
@@ -8601,7 +8628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:16">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>404</v>
       </c>
@@ -8651,7 +8678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:16">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>408</v>
       </c>
@@ -8680,7 +8707,7 @@
         <v>23</v>
       </c>
       <c r="J134" s="1">
-        <v>117.0</v>
+        <v>117</v>
       </c>
       <c r="K134" t="s">
         <v>24</v>
@@ -8701,7 +8728,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:16">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>408</v>
       </c>
@@ -8730,7 +8757,7 @@
         <v>23</v>
       </c>
       <c r="J135" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="K135" t="s">
         <v>59</v>
@@ -8751,7 +8778,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:16">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>408</v>
       </c>
@@ -8780,7 +8807,7 @@
         <v>23</v>
       </c>
       <c r="J136" s="1">
-        <v>268.0</v>
+        <v>268</v>
       </c>
       <c r="K136" t="s">
         <v>59</v>
@@ -8801,7 +8828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:16">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>408</v>
       </c>
@@ -8830,7 +8857,7 @@
         <v>23</v>
       </c>
       <c r="J137" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="K137" t="s">
         <v>59</v>
@@ -8851,7 +8878,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="138" spans="1:16">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>408</v>
       </c>
@@ -8880,7 +8907,7 @@
         <v>23</v>
       </c>
       <c r="J138" s="1">
-        <v>729.0</v>
+        <v>729</v>
       </c>
       <c r="K138" t="s">
         <v>59</v>
@@ -8901,7 +8928,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:16">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>414</v>
       </c>
@@ -8951,7 +8978,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="140" spans="1:16">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>417</v>
       </c>
@@ -9001,7 +9028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="141" spans="1:16">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>417</v>
       </c>
@@ -9051,7 +9078,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="142" spans="1:16">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>420</v>
       </c>
@@ -9101,7 +9128,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="143" spans="1:16">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>423</v>
       </c>
@@ -9130,7 +9157,7 @@
         <v>428</v>
       </c>
       <c r="J143" s="1">
-        <v>438.0</v>
+        <v>438</v>
       </c>
       <c r="K143" t="s">
         <v>176</v>
@@ -9151,7 +9178,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:16">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>423</v>
       </c>
@@ -9180,7 +9207,7 @@
         <v>428</v>
       </c>
       <c r="J144" s="1">
-        <v>191.0</v>
+        <v>191</v>
       </c>
       <c r="K144" t="s">
         <v>59</v>
@@ -9201,7 +9228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:16">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>423</v>
       </c>
@@ -9230,7 +9257,7 @@
         <v>428</v>
       </c>
       <c r="J145" s="1">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="K145" t="s">
         <v>59</v>
@@ -9251,7 +9278,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="146" spans="1:16">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>434</v>
       </c>
@@ -9301,7 +9328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:16">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>437</v>
       </c>
@@ -9351,7 +9378,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="1:16">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>440</v>
       </c>
@@ -9380,7 +9407,7 @@
         <v>23</v>
       </c>
       <c r="J148" s="1">
-        <v>98.0</v>
+        <v>98</v>
       </c>
       <c r="K148" t="s">
         <v>24</v>
@@ -9401,7 +9428,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:16">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>445</v>
       </c>
@@ -9451,7 +9478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:16">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>448</v>
       </c>
@@ -9501,7 +9528,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:16">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>451</v>
       </c>
@@ -9551,7 +9578,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="1:16">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>455</v>
       </c>
@@ -9601,7 +9628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:16">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>459</v>
       </c>
@@ -9630,7 +9657,7 @@
         <v>23</v>
       </c>
       <c r="J153" s="1">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="K153" t="s">
         <v>59</v>
@@ -9651,7 +9678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="154" spans="1:16">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>464</v>
       </c>
@@ -9701,7 +9728,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="155" spans="1:16">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>464</v>
       </c>
@@ -9730,7 +9757,7 @@
         <v>23</v>
       </c>
       <c r="J155" s="1">
-        <v>186.0</v>
+        <v>186</v>
       </c>
       <c r="K155" t="s">
         <v>59</v>
@@ -9751,7 +9778,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="156" spans="1:16">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>471</v>
       </c>
@@ -9801,7 +9828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:16">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>471</v>
       </c>
@@ -9830,7 +9857,7 @@
         <v>23</v>
       </c>
       <c r="J157" s="1">
-        <v>168.0</v>
+        <v>168</v>
       </c>
       <c r="K157" t="s">
         <v>24</v>
@@ -9851,7 +9878,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:16">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>478</v>
       </c>
@@ -9880,7 +9907,7 @@
         <v>23</v>
       </c>
       <c r="J158" s="1">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="K158" t="s">
         <v>24</v>
@@ -9901,7 +9928,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:16">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>483</v>
       </c>
@@ -9930,7 +9957,7 @@
         <v>23</v>
       </c>
       <c r="J159" s="1">
-        <v>33.2</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="K159" t="s">
         <v>24</v>
@@ -9951,7 +9978,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="160" spans="1:16">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>487</v>
       </c>
@@ -10001,7 +10028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="161" spans="1:16">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>491</v>
       </c>
@@ -10051,7 +10078,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="1:16">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>495</v>
       </c>
@@ -10101,7 +10128,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:16">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>499</v>
       </c>
@@ -10151,7 +10178,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:16">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>502</v>
       </c>
@@ -10201,7 +10228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:16">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>505</v>
       </c>
@@ -10251,7 +10278,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="166" spans="1:16">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>510</v>
       </c>
@@ -10301,7 +10328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="167" spans="1:16">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>514</v>
       </c>
@@ -10351,7 +10378,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="168" spans="1:16">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>518</v>
       </c>
@@ -10380,7 +10407,7 @@
         <v>23</v>
       </c>
       <c r="J168" s="1">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="K168" t="s">
         <v>24</v>
@@ -10401,7 +10428,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="169" spans="1:16">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>523</v>
       </c>
@@ -10430,7 +10457,7 @@
         <v>23</v>
       </c>
       <c r="J169" s="1">
-        <v>327.0</v>
+        <v>327</v>
       </c>
       <c r="K169" t="s">
         <v>59</v>
@@ -10451,7 +10478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="170" spans="1:16">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>528</v>
       </c>
@@ -10501,7 +10528,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="171" spans="1:16">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>533</v>
       </c>
@@ -10551,7 +10578,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="172" spans="1:16">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>533</v>
       </c>
@@ -10601,7 +10628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="173" spans="1:16">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>537</v>
       </c>
@@ -10630,7 +10657,7 @@
         <v>23</v>
       </c>
       <c r="J173" s="1">
-        <v>81.6</v>
+        <v>81.599999999999994</v>
       </c>
       <c r="K173" t="s">
         <v>24</v>
@@ -10651,7 +10678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:16">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>541</v>
       </c>
@@ -10701,7 +10728,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:16">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>544</v>
       </c>
@@ -10751,7 +10778,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="176" spans="1:16">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>544</v>
       </c>
@@ -10780,7 +10807,7 @@
         <v>23</v>
       </c>
       <c r="J176" s="1">
-        <v>186.0</v>
+        <v>186</v>
       </c>
       <c r="K176" t="s">
         <v>59</v>
@@ -10802,17 +10829,6 @@
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>